--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N78_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N78_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.83910585037867</v>
+        <v>7.123854700686534</v>
       </c>
       <c r="D2" t="n">
-        <v>43.63727709620859</v>
+        <v>7.091057528133897</v>
       </c>
       <c r="E2" t="n">
-        <v>7.563360538306822</v>
+        <v>1.229046087474858</v>
       </c>
       <c r="F2" t="n">
-        <v>7.463325377973808</v>
+        <v>1.212790373920744</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.84798973570347</v>
+        <v>5.337798332051815</v>
       </c>
       <c r="D3" t="n">
-        <v>32.75600820468657</v>
+        <v>5.322851333261567</v>
       </c>
       <c r="E3" t="n">
-        <v>7.563360538306822</v>
+        <v>1.229046087474858</v>
       </c>
       <c r="F3" t="n">
-        <v>7.463325377973808</v>
+        <v>1.212790373920744</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.79892892172301</v>
+        <v>4.192325949779989</v>
       </c>
       <c r="D4" t="n">
-        <v>26.46394186299457</v>
+        <v>4.300390552736618</v>
       </c>
       <c r="E4" t="n">
-        <v>7.563360538306822</v>
+        <v>1.229046087474858</v>
       </c>
       <c r="F4" t="n">
-        <v>7.463325377973808</v>
+        <v>1.212790373920744</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.56927923986046</v>
+        <v>5.780007876477325</v>
       </c>
       <c r="D5" t="n">
-        <v>35.97143664608079</v>
+        <v>5.845358454988128</v>
       </c>
       <c r="E5" t="n">
-        <v>7.563360538306822</v>
+        <v>1.229046087474858</v>
       </c>
       <c r="F5" t="n">
-        <v>7.463325377973808</v>
+        <v>1.212790373920744</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.83699213117637</v>
+        <v>5.823511221316161</v>
       </c>
       <c r="D6" t="n">
-        <v>35.91941149763576</v>
+        <v>5.836904368365812</v>
       </c>
       <c r="E6" t="n">
-        <v>7.563360538306822</v>
+        <v>1.229046087474858</v>
       </c>
       <c r="F6" t="n">
-        <v>7.463325377973808</v>
+        <v>1.212790373920744</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.2174027453264</v>
+        <v>2.79782794611554</v>
       </c>
       <c r="D7" t="n">
-        <v>17.0316906538294</v>
+        <v>2.767649731247278</v>
       </c>
       <c r="E7" t="n">
-        <v>7.563360538306822</v>
+        <v>1.229046087474858</v>
       </c>
       <c r="F7" t="n">
-        <v>7.463325377973808</v>
+        <v>1.212790373920744</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>34.41349315718266</v>
+        <v>5.592192638042183</v>
       </c>
       <c r="D8" t="n">
-        <v>34.55883963137028</v>
+        <v>5.615811440097671</v>
       </c>
       <c r="E8" t="n">
-        <v>7.563360538306822</v>
+        <v>1.229046087474858</v>
       </c>
       <c r="F8" t="n">
-        <v>7.463325377973808</v>
+        <v>1.212790373920744</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>48.412561883717</v>
+        <v>7.867041306104012</v>
       </c>
       <c r="D9" t="n">
-        <v>47.67114398181864</v>
+        <v>7.746560897045529</v>
       </c>
       <c r="E9" t="n">
-        <v>7.563360538306822</v>
+        <v>1.229046087474858</v>
       </c>
       <c r="F9" t="n">
-        <v>7.463325377973808</v>
+        <v>1.212790373920744</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.91468466995221</v>
+        <v>5.186136258867235</v>
       </c>
       <c r="D10" t="n">
-        <v>31.16132185740372</v>
+        <v>5.063714801828105</v>
       </c>
       <c r="E10" t="n">
-        <v>7.563360538306822</v>
+        <v>1.229046087474858</v>
       </c>
       <c r="F10" t="n">
-        <v>7.463325377973808</v>
+        <v>1.212790373920744</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.22741208804545</v>
+        <v>5.561954464307385</v>
       </c>
       <c r="D11" t="n">
-        <v>34.04589315755277</v>
+        <v>5.532457638102325</v>
       </c>
       <c r="E11" t="n">
-        <v>7.563360538306822</v>
+        <v>1.229046087474858</v>
       </c>
       <c r="F11" t="n">
-        <v>7.463325377973808</v>
+        <v>1.212790373920744</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>37.08749422659078</v>
+        <v>6.026717811821001</v>
       </c>
       <c r="D12" t="n">
-        <v>37.33813464951452</v>
+        <v>6.06744688054611</v>
       </c>
       <c r="E12" t="n">
-        <v>7.563360538306822</v>
+        <v>1.229046087474858</v>
       </c>
       <c r="F12" t="n">
-        <v>7.463325377973808</v>
+        <v>1.212790373920744</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>38.00298821037486</v>
+        <v>6.175485584185915</v>
       </c>
       <c r="D13" t="n">
-        <v>38.39462807943813</v>
+        <v>6.239127062908696</v>
       </c>
       <c r="E13" t="n">
-        <v>7.563360538306822</v>
+        <v>1.229046087474858</v>
       </c>
       <c r="F13" t="n">
-        <v>7.463325377973808</v>
+        <v>1.212790373920744</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
